--- a/Result/profitability/1235.xlsx
+++ b/Result/profitability/1235.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.12</v>
+        <v>-0.1025</v>
       </c>
       <c r="N2" t="n">
-        <v>27.105</v>
+        <v>27.5625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.13125</v>
+        <v>0.17</v>
       </c>
       <c r="N3" t="n">
-        <v>25.81625</v>
+        <v>25.29875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08875000000000005</v>
+        <v>0.1775</v>
       </c>
       <c r="N4" t="n">
-        <v>23.62375</v>
+        <v>23.26875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.74</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01874999999999995</v>
+        <v>0.01000000000000004</v>
       </c>
       <c r="N5" t="n">
-        <v>20.3575</v>
+        <v>21.25125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1137499999999999</v>
+        <v>-0.01749999999999996</v>
       </c>
       <c r="N6" t="n">
-        <v>18.00625</v>
+        <v>18.29125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.09874999999999994</v>
+        <v>0.09125000000000003</v>
       </c>
       <c r="N7" t="n">
-        <v>16.08625</v>
+        <v>16.47</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.01999999999999994</v>
+        <v>0.1512500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>14.0675</v>
+        <v>14.28125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.36</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09250000000000005</v>
+        <v>0.09250000000000004</v>
       </c>
       <c r="N9" t="n">
         <v>11.94875</v>
@@ -1645,7 +1645,7 @@
         <v>0.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04625000000000005</v>
+        <v>0.04625000000000004</v>
       </c>
       <c r="N10" t="n">
         <v>11.36</v>
@@ -1772,7 +1772,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.01999999999999994</v>
+        <v>-0.01999999999999996</v>
       </c>
       <c r="N11" t="n">
         <v>10.8575</v>
@@ -1899,7 +1899,7 @@
         <v>0.42</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01000000000000006</v>
+        <v>0.01000000000000004</v>
       </c>
       <c r="N12" t="n">
         <v>10.12375</v>
@@ -2026,7 +2026,7 @@
         <v>-0.21</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07625000000000007</v>
+        <v>0.07625000000000004</v>
       </c>
       <c r="N13" t="n">
         <v>10.18</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>34</v>
+      </c>
+      <c r="D75" t="n">
+        <v>24</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-18.89%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>166</v>
+      </c>
+      <c r="J75" t="n">
+        <v>159</v>
+      </c>
+      <c r="K75" t="n">
+        <v>90</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.06374999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.89875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.537037037037037</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.710000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05989492119089324</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3833333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.150000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3093898745131978</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
